--- a/data_info.xlsx
+++ b/data_info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lixiang/Documents/Doragroup/papers/MACHINE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lixiang/Documents/Doragroup/papers/MACHINE/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96390042-47F0-7E47-B52E-B12186BE655E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3001D1F-DBE4-5E4C-ABFB-CD7024344064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{0F0D3BED-B3F2-924A-9724-74E0EE24C599}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{0F0D3BED-B3F2-924A-9724-74E0EE24C599}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>Supplementary Table</t>
   </si>
@@ -44,30 +44,12 @@
     <t>Figure</t>
   </si>
   <si>
-    <t>S2,S14</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>S18-20</t>
-  </si>
-  <si>
-    <t>S21-22</t>
-  </si>
-  <si>
     <t>S23</t>
   </si>
   <si>
-    <t>3c-f</t>
-  </si>
-  <si>
     <t>Ex3a</t>
   </si>
   <si>
-    <t>Ex3b-e</t>
-  </si>
-  <si>
     <t>Script</t>
   </si>
   <si>
@@ -83,9 +65,6 @@
     <t>S5</t>
   </si>
   <si>
-    <t>S10</t>
-  </si>
-  <si>
     <t>simulation/plot_FDR_power.R</t>
   </si>
   <si>
@@ -131,57 +110,18 @@
     <t>simulation/results/calibration_1kG.pdf</t>
   </si>
   <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>S9</t>
-  </si>
-  <si>
-    <t>simulation/results/var_wilcox_p_UKBB.pdf</t>
-  </si>
-  <si>
-    <t>simulation/results/var_wilcox_p_1kG.pdf</t>
-  </si>
-  <si>
-    <t>S4</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
     <t>simulation/results/power_improvement.RData</t>
   </si>
   <si>
-    <t>simulation/results/var_wilcox_p_UKBB.RData</t>
-  </si>
-  <si>
-    <t>simulation/results/var_wilcox_p_1kG.RData</t>
-  </si>
-  <si>
     <t>simulation/plot_anno_var.R</t>
   </si>
   <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>simulation/results/var_violin_UKBB.pdf</t>
-  </si>
-  <si>
     <t>simulation/results/coverage-size_UKBB.pdf</t>
   </si>
   <si>
     <t>simulation/results/coverage-size_1kG.pdf</t>
   </si>
   <si>
-    <t>S6-8</t>
-  </si>
-  <si>
-    <t>S11-13</t>
-  </si>
-  <si>
     <t>simulation/plot_coverage-size.R</t>
   </si>
   <si>
@@ -212,9 +152,6 @@
     <t>simulation/results/computing_time_model_info.RData</t>
   </si>
   <si>
-    <t>3a,b</t>
-  </si>
-  <si>
     <t>real_data/glgc/RFR_eQTL_enrichment.pdf</t>
   </si>
   <si>
@@ -287,12 +224,6 @@
     <t>real_data/glgc/examples/example_3.pdf</t>
   </si>
   <si>
-    <t>Ex2</t>
-  </si>
-  <si>
-    <t>Ex1</t>
-  </si>
-  <si>
     <t>real_data/scz2022/plot_CS_overlap.R</t>
   </si>
   <si>
@@ -315,6 +246,117 @@
   </si>
   <si>
     <t>real_data/scz2022/examples/example_1.pdf</t>
+  </si>
+  <si>
+    <t>2,Ex1</t>
+  </si>
+  <si>
+    <t>3,Ex2</t>
+  </si>
+  <si>
+    <t>S6-7</t>
+  </si>
+  <si>
+    <t>S14-15</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>simulation_new/results/single_ancestry.pdf</t>
+  </si>
+  <si>
+    <t>simulation_new/results/multi_ancestry.pdf</t>
+  </si>
+  <si>
+    <t>simulation/plot_single_ancestry.R</t>
+  </si>
+  <si>
+    <t>simulation/plot_multi_ancestry.R</t>
+  </si>
+  <si>
+    <t>S1-2</t>
+  </si>
+  <si>
+    <t>S11-12</t>
+  </si>
+  <si>
+    <t>S3,S19</t>
+  </si>
+  <si>
+    <t>simulation/results/var_wilcox_p.Rdata</t>
+  </si>
+  <si>
+    <t>simulation/results/var_wilcox_p.pdf</t>
+  </si>
+  <si>
+    <t>S8-10</t>
+  </si>
+  <si>
+    <t>S16-18</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>simulation/results/var_violin.pdf</t>
+  </si>
+  <si>
+    <t>S4,S20</t>
+  </si>
+  <si>
+    <t>simulation/results/LD_compare.pdf</t>
+  </si>
+  <si>
+    <t>simulation/plot_LD_compare.R</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>simulation/plot_lambda.R</t>
+  </si>
+  <si>
+    <t>simulation/results/lambda.pdf</t>
+  </si>
+  <si>
+    <t>4a-b,e-h</t>
+  </si>
+  <si>
+    <t>4c-d</t>
+  </si>
+  <si>
+    <t>S25-27</t>
+  </si>
+  <si>
+    <t>S28-29</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Ex3</t>
+  </si>
+  <si>
+    <t>Ex4</t>
+  </si>
+  <si>
+    <t>Ex3b-f</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>real_data/computing_time_model_info.Rdata</t>
+  </si>
+  <si>
+    <t>real_data/computing_time.pdf</t>
+  </si>
+  <si>
+    <t>real_data/plot_computing_time.R</t>
   </si>
 </sst>
 </file>
@@ -356,13 +398,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -698,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12199DF5-4A70-BC4C-96A1-47665FB8A0E8}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
@@ -719,13 +764,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -734,11 +779,11 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -747,155 +792,157 @@
       <c r="C3" s="2"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
-        <v>2</v>
+      <c r="B4" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="1">
-        <v>3</v>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>3</v>
-      </c>
+      <c r="A8" s="2"/>
       <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C8" s="2"/>
       <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>75</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>5</v>
+      </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -904,276 +951,330 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>7</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>10</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
+      <c r="B26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>11</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
+      <c r="B27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>12</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
+      <c r="B28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>13</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
-        <v>83</v>
+      <c r="B30" s="1">
+        <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>14</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+      <c r="B33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>15</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1">
-        <v>5</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>90</v>
+      <c r="B34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>16</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="23">
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="E21:E22"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="A15:A16"/>
@@ -1181,23 +1282,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="A4:A9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
